--- a/IPE2/EXCEL CUENTAS ANUALES.xlsx
+++ b/IPE2/EXCEL CUENTAS ANUALES.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\YEHORBURLACHENKO\AulaCampus2\IPE2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{94438C1B-0FC3-434A-B11A-4C203F138AE7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0939A4DA-3BF7-46DB-996F-C492BEE33A7C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Estados Financieros" sheetId="2" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="54">
   <si>
     <t>A-(PN+P)</t>
   </si>
@@ -129,9 +129,6 @@
     <t>Pasivo No Corriente (Deudas a largo plazo &gt; 1 año)</t>
   </si>
   <si>
-    <t>Gastos bancarios</t>
-  </si>
-  <si>
     <t>Bancos, cajas, entidades financieras a largo plazo</t>
   </si>
   <si>
@@ -160,9 +157,6 @@
   </si>
   <si>
     <t xml:space="preserve">Materias Primas </t>
-  </si>
-  <si>
-    <t>Seguros</t>
   </si>
   <si>
     <r>
@@ -254,9 +248,6 @@
     <t>Mobiliario de puesto de trabajo</t>
   </si>
   <si>
-    <t>Equipos informáticos y dispositivos de desarrollo</t>
-  </si>
-  <si>
     <t>Software, licencias y herramientas digitales</t>
   </si>
   <si>
@@ -266,10 +257,16 @@
     <t>Desarrollo inicial del producto y activos intangibles</t>
   </si>
   <si>
-    <t>Servicios digitales a corto plazo (cloud, SaaS)</t>
-  </si>
-  <si>
     <t>Tesorería inicial en banco o caja</t>
+  </si>
+  <si>
+    <t>Equipos informáticos y dispositivos de desarrollo, cloud</t>
+  </si>
+  <si>
+    <t>Cuota autonomo(tarifa plana)</t>
+  </si>
+  <si>
+    <t>Seguro de responsabilidad civil profesional</t>
   </si>
 </sst>
 </file>
@@ -279,7 +276,7 @@
   <numFmts count="1">
     <numFmt numFmtId="44" formatCode="_-* #,##0.00\ &quot;€&quot;_-;\-* #,##0.00\ &quot;€&quot;_-;_-* &quot;-&quot;??\ &quot;€&quot;_-;_-@_-"/>
   </numFmts>
-  <fonts count="14" x14ac:knownFonts="1">
+  <fonts count="15" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -358,6 +355,12 @@
       <sz val="10"/>
       <name val="Arial"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="6">
     <fill>
@@ -733,7 +736,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="44" fontId="13" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="55">
+  <cellXfs count="60">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -826,33 +829,6 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="44" fontId="1" fillId="3" borderId="16" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
@@ -880,12 +856,54 @@
     <xf numFmtId="44" fontId="1" fillId="2" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="44" fontId="2" fillId="3" borderId="20" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="44" fontId="2" fillId="3" borderId="19" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="44" fontId="1" fillId="4" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="44" fontId="14" fillId="4" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Moneda" xfId="1" builtinId="4"/>
@@ -1445,17 +1463,17 @@
     </row>
     <row r="7" spans="1:10" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="9"/>
-      <c r="B7" s="36" t="s">
+      <c r="B7" s="44" t="s">
         <v>3</v>
       </c>
-      <c r="C7" s="37"/>
-      <c r="D7" s="37"/>
-      <c r="E7" s="38"/>
+      <c r="C7" s="45"/>
+      <c r="D7" s="45"/>
+      <c r="E7" s="46"/>
       <c r="F7" s="9"/>
-      <c r="G7" s="36" t="s">
+      <c r="G7" s="44" t="s">
         <v>4</v>
       </c>
-      <c r="H7" s="38"/>
+      <c r="H7" s="46"/>
       <c r="I7" s="9"/>
       <c r="J7" s="9"/>
     </row>
@@ -1497,15 +1515,15 @@
         <v>9</v>
       </c>
       <c r="C10" s="30"/>
-      <c r="D10" s="41" t="s">
+      <c r="D10" s="51" t="s">
         <v>10</v>
       </c>
-      <c r="E10" s="42"/>
+      <c r="E10" s="52"/>
       <c r="F10" s="9"/>
-      <c r="G10" s="41" t="s">
+      <c r="G10" s="51" t="s">
         <v>11</v>
       </c>
-      <c r="H10" s="42"/>
+      <c r="H10" s="52"/>
       <c r="I10" s="9"/>
       <c r="J10" s="9"/>
     </row>
@@ -1514,14 +1532,14 @@
       <c r="B11" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="C11" s="46">
+      <c r="C11" s="37">
         <f>SUM(C12:C19)</f>
-        <v>10000</v>
+        <v>11000</v>
       </c>
       <c r="D11" s="26" t="s">
         <v>13</v>
       </c>
-      <c r="E11" s="49">
+      <c r="E11" s="40">
         <f>SUM(E12:E15)</f>
         <v>15000</v>
       </c>
@@ -1536,22 +1554,22 @@
     <row r="12" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="9"/>
       <c r="B12" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="C12" s="47">
+        <v>43</v>
+      </c>
+      <c r="C12" s="38">
         <v>0</v>
       </c>
       <c r="D12" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="E12" s="47">
+      <c r="E12" s="38">
         <v>15000</v>
       </c>
       <c r="F12" s="9"/>
       <c r="G12" s="21" t="s">
         <v>16</v>
       </c>
-      <c r="H12" s="50">
+      <c r="H12" s="41">
         <v>18000</v>
       </c>
       <c r="I12" s="9"/>
@@ -1560,20 +1578,20 @@
     <row r="13" spans="1:10" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="9"/>
       <c r="B13" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="C13" s="47">
+        <v>44</v>
+      </c>
+      <c r="C13" s="38">
         <v>500</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="E13" s="5"/>
       <c r="F13" s="9"/>
       <c r="G13" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="H13" s="51">
+      <c r="H13" s="42">
         <v>0</v>
       </c>
       <c r="I13" s="9"/>
@@ -1582,9 +1600,9 @@
     <row r="14" spans="1:10" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="9"/>
       <c r="B14" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="C14" s="47">
+        <v>45</v>
+      </c>
+      <c r="C14" s="38">
         <v>700</v>
       </c>
       <c r="D14" s="6"/>
@@ -1593,7 +1611,7 @@
       <c r="G14" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="H14" s="47">
+      <c r="H14" s="38">
         <v>600</v>
       </c>
       <c r="I14" s="9"/>
@@ -1602,9 +1620,9 @@
     <row r="15" spans="1:10" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="9"/>
       <c r="B15" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="C15" s="47">
+        <v>46</v>
+      </c>
+      <c r="C15" s="38">
         <v>600</v>
       </c>
       <c r="D15" s="6"/>
@@ -1613,7 +1631,7 @@
       <c r="G15" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="H15" s="47">
+      <c r="H15" s="38">
         <v>200</v>
       </c>
       <c r="I15" s="9"/>
@@ -1622,24 +1640,24 @@
     <row r="16" spans="1:10" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="9"/>
       <c r="B16" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="C16" s="45">
-        <v>2200</v>
+        <v>51</v>
+      </c>
+      <c r="C16" s="36">
+        <v>3200</v>
       </c>
       <c r="D16" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="E16" s="49">
+      <c r="E16" s="40">
         <f>SUM(E17:E22)</f>
         <v>0</v>
       </c>
       <c r="F16" s="9"/>
-      <c r="G16" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="H16" s="47">
-        <v>150</v>
+      <c r="G16" s="58" t="s">
+        <v>52</v>
+      </c>
+      <c r="H16" s="57">
+        <v>960</v>
       </c>
       <c r="I16" s="9"/>
       <c r="J16" s="9"/>
@@ -1647,22 +1665,22 @@
     <row r="17" spans="1:10" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="9"/>
       <c r="B17" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="C17" s="47">
+        <v>47</v>
+      </c>
+      <c r="C17" s="38">
         <v>2000</v>
       </c>
       <c r="D17" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="E17" s="47">
+        <v>21</v>
+      </c>
+      <c r="E17" s="38">
         <v>0</v>
       </c>
       <c r="F17" s="9"/>
       <c r="G17" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="H17" s="47">
+        <v>22</v>
+      </c>
+      <c r="H17" s="38">
         <v>1200</v>
       </c>
       <c r="I17" s="9"/>
@@ -1671,22 +1689,22 @@
     <row r="18" spans="1:10" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="9"/>
       <c r="B18" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="C18" s="47">
+        <v>48</v>
+      </c>
+      <c r="C18" s="38">
         <v>0</v>
       </c>
       <c r="D18" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="E18" s="47">
+        <v>23</v>
+      </c>
+      <c r="E18" s="38">
         <v>0</v>
       </c>
       <c r="F18" s="9"/>
       <c r="G18" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="H18" s="47">
+        <v>24</v>
+      </c>
+      <c r="H18" s="38">
         <v>12000</v>
       </c>
       <c r="I18" s="9"/>
@@ -1695,45 +1713,45 @@
     <row r="19" spans="1:10" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="9"/>
       <c r="B19" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="C19" s="47">
+        <v>49</v>
+      </c>
+      <c r="C19" s="38">
         <v>4000</v>
       </c>
       <c r="D19" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="E19" s="47">
+        <v>25</v>
+      </c>
+      <c r="E19" s="38">
         <v>0</v>
       </c>
       <c r="F19" s="9"/>
       <c r="G19" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="H19" s="47"/>
+        <v>26</v>
+      </c>
+      <c r="H19" s="38"/>
       <c r="I19" s="9"/>
       <c r="J19" s="9"/>
     </row>
     <row r="20" spans="1:10" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="9"/>
       <c r="B20" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="C20" s="37">
+        <f>SUM(C21:C27)</f>
+        <v>4000</v>
+      </c>
+      <c r="D20" s="27" t="s">
         <v>28</v>
       </c>
-      <c r="C20" s="46">
-        <f>SUM(C21:C27)</f>
-        <v>5000</v>
-      </c>
-      <c r="D20" s="27" t="s">
-        <v>29</v>
-      </c>
-      <c r="E20" s="47">
+      <c r="E20" s="38">
         <v>0</v>
       </c>
       <c r="F20" s="9"/>
       <c r="G20" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="H20" s="47">
+        <v>29</v>
+      </c>
+      <c r="H20" s="38">
         <v>1500</v>
       </c>
       <c r="I20" s="9"/>
@@ -1742,20 +1760,20 @@
     <row r="21" spans="1:10" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="9"/>
       <c r="B21" s="22" t="s">
-        <v>31</v>
-      </c>
-      <c r="C21" s="47">
+        <v>30</v>
+      </c>
+      <c r="C21" s="38">
         <v>0</v>
       </c>
       <c r="D21" s="6"/>
-      <c r="E21" s="47">
+      <c r="E21" s="38">
         <v>0</v>
       </c>
       <c r="F21" s="9"/>
-      <c r="G21" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="H21" s="47">
+      <c r="G21" s="55" t="s">
+        <v>53</v>
+      </c>
+      <c r="H21" s="56">
         <v>250</v>
       </c>
       <c r="I21" s="9"/>
@@ -1764,18 +1782,18 @@
     <row r="22" spans="1:10" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="9"/>
       <c r="B22" s="23" t="s">
-        <v>33</v>
-      </c>
-      <c r="C22" s="48">
+        <v>31</v>
+      </c>
+      <c r="C22" s="39">
         <v>0</v>
       </c>
       <c r="D22" s="6"/>
       <c r="E22" s="5"/>
       <c r="F22" s="9"/>
       <c r="G22" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="H22" s="47">
+        <v>32</v>
+      </c>
+      <c r="H22" s="38">
         <v>0</v>
       </c>
       <c r="I22" s="9"/>
@@ -1783,24 +1801,24 @@
     </row>
     <row r="23" spans="1:10" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="9"/>
-      <c r="B23" s="23" t="s">
-        <v>53</v>
-      </c>
-      <c r="C23" s="47">
-        <v>1000</v>
+      <c r="B23" s="28" t="s">
+        <v>50</v>
+      </c>
+      <c r="C23" s="38">
+        <v>4000</v>
       </c>
       <c r="D23" s="13" t="s">
-        <v>35</v>
-      </c>
-      <c r="E23" s="49">
+        <v>33</v>
+      </c>
+      <c r="E23" s="40">
         <f>SUM(E24:E27)</f>
         <v>0</v>
       </c>
       <c r="F23" s="9"/>
       <c r="G23" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="H23" s="47">
+        <v>34</v>
+      </c>
+      <c r="H23" s="38">
         <v>300</v>
       </c>
       <c r="I23" s="9"/>
@@ -1808,23 +1826,19 @@
     </row>
     <row r="24" spans="1:10" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="9"/>
-      <c r="B24" s="28" t="s">
-        <v>54</v>
-      </c>
-      <c r="C24" s="47">
-        <v>4000</v>
-      </c>
+      <c r="B24" s="28"/>
+      <c r="C24" s="38"/>
       <c r="D24" s="6"/>
-      <c r="E24" s="47">
+      <c r="E24" s="38">
         <v>0</v>
       </c>
       <c r="F24" s="9"/>
       <c r="G24" s="31" t="s">
-        <v>37</v>
-      </c>
-      <c r="H24" s="52">
+        <v>35</v>
+      </c>
+      <c r="H24" s="43">
         <f>SUM(H13:H23)</f>
-        <v>16200</v>
+        <v>17010</v>
       </c>
       <c r="I24" s="9"/>
       <c r="J24" s="9"/>
@@ -1834,18 +1848,18 @@
       <c r="B25" s="35"/>
       <c r="C25" s="5"/>
       <c r="D25" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="E25" s="47">
+        <v>36</v>
+      </c>
+      <c r="E25" s="38">
         <v>0</v>
       </c>
       <c r="F25" s="9"/>
-      <c r="G25" s="43" t="s">
-        <v>39</v>
-      </c>
-      <c r="H25" s="53">
+      <c r="G25" s="53" t="s">
+        <v>37</v>
+      </c>
+      <c r="H25" s="49">
         <f>H12-H24</f>
-        <v>1800</v>
+        <v>990</v>
       </c>
       <c r="I25" s="9"/>
       <c r="J25" s="9"/>
@@ -1855,14 +1869,14 @@
       <c r="B26" s="6"/>
       <c r="C26" s="5"/>
       <c r="D26" s="8" t="s">
-        <v>40</v>
-      </c>
-      <c r="E26" s="47">
+        <v>38</v>
+      </c>
+      <c r="E26" s="38">
         <v>0</v>
       </c>
       <c r="F26" s="9"/>
-      <c r="G26" s="44"/>
-      <c r="H26" s="54"/>
+      <c r="G26" s="54"/>
+      <c r="H26" s="50"/>
       <c r="I26" s="9"/>
       <c r="J26" s="9"/>
     </row>
@@ -1881,24 +1895,24 @@
     <row r="28" spans="1:10" ht="15" x14ac:dyDescent="0.2">
       <c r="A28" s="9"/>
       <c r="B28" s="15" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C28" s="25">
         <f>C11+C20</f>
         <v>15000</v>
       </c>
       <c r="D28" s="34" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E28" s="32">
         <f>E11+E16+E23</f>
         <v>15000</v>
       </c>
       <c r="F28" s="9"/>
-      <c r="G28" s="39" t="s">
-        <v>43</v>
-      </c>
-      <c r="H28" s="40"/>
+      <c r="G28" s="47" t="s">
+        <v>41</v>
+      </c>
+      <c r="H28" s="48"/>
       <c r="I28" s="9"/>
       <c r="J28" s="9"/>
     </row>
@@ -1928,7 +1942,7 @@
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A31" s="9"/>
-      <c r="B31" s="9"/>
+      <c r="B31" s="59"/>
       <c r="C31" s="9"/>
       <c r="D31" s="9"/>
       <c r="E31" s="9"/>
@@ -2113,6 +2127,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <TaxCatchAll xmlns="9861335f-2f0b-43dd-a468-b0ac7dd8fca1" xsi:nil="true"/>
@@ -2121,15 +2144,6 @@
     </lcf76f155ced4ddcb4097134ff3c332f>
   </documentManagement>
 </p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2334,20 +2348,20 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0C82DA85-6E85-43AE-B66A-E81C6042D2D1}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FD6F4400-B977-4A55-BEA8-E266C33AA2F0}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     <ds:schemaRef ds:uri="9861335f-2f0b-43dd-a468-b0ac7dd8fca1"/>
     <ds:schemaRef ds:uri="b491b4d8-014e-44b4-b681-9b295da05eef"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0C82DA85-6E85-43AE-B66A-E81C6042D2D1}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
